--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571538824</v>
+        <v>46157.93109318479</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93109318479</v>
+        <v>46157.93178311859</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178311859</v>
+        <v>46157.93403131325</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93403131325</v>
+        <v>46157.93721105052</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93721105052</v>
+        <v>46158.28219136809</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219136809</v>
+        <v>46158.29693717806</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29693717806</v>
+        <v>46158.29818426528</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29818426528</v>
+        <v>46158.33390117733</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33390117733</v>
+        <v>46158.36859966101</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859966101</v>
+        <v>46158.37290569695</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
